--- a/outputs/analyses/uncertainty-loo/final-tables/table_bootstrap_final_summary.xlsx
+++ b/outputs/analyses/uncertainty-loo/final-tables/table_bootstrap_final_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\Caribbean-CVA\outputs\analyses\uncertainty-loo\final-tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{4F56F9F7-F77F-43C0-9FB5-E8A789F66BFC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BA349A1D-35CD-4DCE-8289-7A13ADEDE7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1185" yWindow="1800" windowWidth="20130" windowHeight="13350" xr2:uid="{22C582EC-0CD4-4B4E-A343-24A0A8675FB9}"/>
+    <workbookView xWindow="4860" yWindow="2130" windowWidth="20130" windowHeight="13350" xr2:uid="{22C582EC-0CD4-4B4E-A343-24A0A8675FB9}"/>
   </bookViews>
   <sheets>
     <sheet name="table_bootstrap_final_summary" sheetId="1" r:id="rId1"/>
@@ -112,9 +112,6 @@
     <t>Queen Conch</t>
   </si>
   <si>
-    <t>Atlantic Hherring</t>
-  </si>
-  <si>
     <t>Blue Runner</t>
   </si>
   <si>
@@ -128,6 +125,9 @@
   </si>
   <si>
     <t>White Mullet</t>
+  </si>
+  <si>
+    <t>Atlantic Herring</t>
   </si>
 </sst>
 </file>
@@ -1741,7 +1741,7 @@
     </row>
     <row r="20" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A20" s="30" t="s">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2">
         <v>7</v>
@@ -1799,7 +1799,7 @@
     </row>
     <row r="22" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A22" s="30" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B22" s="2">
         <v>8</v>
@@ -1857,7 +1857,7 @@
     </row>
     <row r="24" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A24" s="30" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B24" s="2">
         <v>9</v>
@@ -1886,7 +1886,7 @@
     </row>
     <row r="25" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A25" s="30" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B25" s="2">
         <v>6</v>
@@ -1915,7 +1915,7 @@
     </row>
     <row r="26" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A26" s="30" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2">
         <v>6</v>
@@ -1944,7 +1944,7 @@
     </row>
     <row r="27" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
       <c r="A27" s="32" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B27" s="16">
         <v>4</v>
@@ -1994,5 +1994,6 @@
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>
--- a/outputs/analyses/uncertainty-loo/final-tables/table_bootstrap_final_summary.xlsx
+++ b/outputs/analyses/uncertainty-loo/final-tables/table_bootstrap_final_summary.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Repos\Caribbean-CVA\outputs\analyses\uncertainty-loo\final-tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{BA349A1D-35CD-4DCE-8289-7A13ADEDE7CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6F81F366-211F-4439-95CA-2CED8FCFA13C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4860" yWindow="2130" windowWidth="20130" windowHeight="13350" xr2:uid="{22C582EC-0CD4-4B4E-A343-24A0A8675FB9}"/>
+    <workbookView xWindow="30930" yWindow="2040" windowWidth="17685" windowHeight="12960" xr2:uid="{9185D89D-DEE3-4438-94E6-30311B95A114}"/>
   </bookViews>
   <sheets>
     <sheet name="table_bootstrap_final_summary" sheetId="1" r:id="rId1"/>
@@ -49,92 +49,92 @@
     <t>VH</t>
   </si>
   <si>
+    <t>Ballyhoo</t>
+  </si>
+  <si>
+    <t>Dolphinfish</t>
+  </si>
+  <si>
+    <t>Overall Ranks</t>
+  </si>
+  <si>
+    <t>Bootstrap Results</t>
+  </si>
+  <si>
     <t>Hogfish</t>
   </si>
   <si>
-    <t>Ballyhoo</t>
-  </si>
-  <si>
-    <t>Dolphinfish</t>
-  </si>
-  <si>
-    <t>Bootstrap Results</t>
-  </si>
-  <si>
     <t>Diadema</t>
   </si>
   <si>
-    <t>Overall Ranks</t>
+    <t>Gray Angelfish</t>
+  </si>
+  <si>
+    <t>Misty Grouper</t>
+  </si>
+  <si>
+    <t>Mutton Snapper</t>
+  </si>
+  <si>
+    <t>Nassau Grouper</t>
+  </si>
+  <si>
+    <t>Queen Conch</t>
   </si>
   <si>
     <t>Rainbow Parrotfish</t>
   </si>
   <si>
-    <t>Mutton Snapper</t>
-  </si>
-  <si>
-    <t>Nassau Grouper</t>
+    <t>Red Grouper</t>
+  </si>
+  <si>
+    <t>Red Hind</t>
+  </si>
+  <si>
+    <t>Stoplight Parrotfish</t>
+  </si>
+  <si>
+    <t>Yellowfin Grouper</t>
   </si>
   <si>
     <t>Lane Snapper</t>
   </si>
   <si>
-    <t>Misty Grouper</t>
-  </si>
-  <si>
     <t>Queen Triggerfish</t>
   </si>
   <si>
-    <t>Gray Angelfish</t>
-  </si>
-  <si>
-    <t>Sea Cucumber</t>
-  </si>
-  <si>
-    <t>Stoplight Parrotfish</t>
+    <t>Sea Cucumbers</t>
+  </si>
+  <si>
+    <t>Yellowtail Snapper </t>
+  </si>
+  <si>
+    <t>King Mackerel</t>
+  </si>
+  <si>
+    <t>Queen Snapper</t>
+  </si>
+  <si>
+    <t>Silk Snapper</t>
   </si>
   <si>
     <t>Spiny Lobster</t>
   </si>
   <si>
-    <t>Redhind</t>
-  </si>
-  <si>
-    <t>Red Grouper</t>
-  </si>
-  <si>
-    <t>Yellowtail Snapper</t>
-  </si>
-  <si>
-    <t>Yellowfin Grouper </t>
-  </si>
-  <si>
-    <t>Queen Conch</t>
+    <t>Atlantic Herring</t>
   </si>
   <si>
     <t>Blue Runner</t>
   </si>
   <si>
-    <t>King Mackerel</t>
-  </si>
-  <si>
-    <t>Queen Snapper</t>
-  </si>
-  <si>
-    <t>Silk Snapper</t>
-  </si>
-  <si>
     <t>White Mullet</t>
-  </si>
-  <si>
-    <t>Atlantic Herring</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -270,19 +270,13 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
     <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Arial"/>
@@ -471,6 +465,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.89999084444715716"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -493,14 +493,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="3" tint="0.89999084444715716"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="12">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -633,6 +627,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="dashed">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -678,118 +681,58 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="35" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="36" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="36" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="37" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="19" fillId="34" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="2" fontId="18" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="33" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="35" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="19" fillId="36" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="36" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="19" fillId="37" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="19" fillId="33" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="2" fontId="19" fillId="37" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="19" fillId="34" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -835,14 +778,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="4">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill>
@@ -861,6 +797,20 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFFF00"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FF92D050"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1193,804 +1143,807 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B14A5C29-0338-4DBA-8B44-3B57F6D6DD2A}">
-  <dimension ref="A1:I27"/>
-  <sheetFormatPr defaultRowHeight="12" x14ac:dyDescent="0.2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F6594131-4C70-468B-B1CC-AA4DE240B590}">
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.42578125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.85546875" style="29" customWidth="1"/>
-    <col min="3" max="16384" width="9.140625" style="1"/>
+    <col min="1" max="1" width="22.5703125" style="5" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" style="7" customWidth="1"/>
+    <col min="3" max="5" width="9.140625" style="7"/>
+    <col min="6" max="16384" width="9.140625" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" x14ac:dyDescent="0.25">
-      <c r="A1" s="14"/>
-      <c r="B1" s="14"/>
-      <c r="C1" s="15" t="s">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+    </row>
+    <row r="2" spans="1:9" ht="30" x14ac:dyDescent="0.2">
+      <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>5</v>
+      </c>
+      <c r="G2" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="H2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="I2" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="15"/>
-      <c r="E1" s="15"/>
-      <c r="F1" s="15" t="s">
+      <c r="B3" s="7">
+        <v>11</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5">
+        <v>0</v>
+      </c>
+      <c r="G3" s="5">
+        <v>0</v>
+      </c>
+      <c r="H3" s="5">
+        <v>0</v>
+      </c>
+      <c r="I3" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="B4" s="7">
+        <v>7</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E4" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="5">
+        <v>0</v>
+      </c>
+      <c r="G4" s="5">
+        <v>0</v>
+      </c>
+      <c r="H4" s="5">
+        <v>0</v>
+      </c>
+      <c r="I4" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="6" t="s">
+        <v>17</v>
+      </c>
+      <c r="B5" s="7">
+        <v>11</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F5" s="5">
+        <v>0</v>
+      </c>
+      <c r="G5" s="5">
+        <v>0</v>
+      </c>
+      <c r="H5" s="5">
+        <v>0</v>
+      </c>
+      <c r="I5" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="7">
+        <v>8</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D6" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E6" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5">
+        <v>0</v>
+      </c>
+      <c r="G6" s="5">
+        <v>0</v>
+      </c>
+      <c r="H6" s="5">
+        <v>0</v>
+      </c>
+      <c r="I6" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="6" t="s">
+        <v>19</v>
+      </c>
+      <c r="B7" s="7">
         <v>12</v>
       </c>
-      <c r="G1" s="15"/>
-      <c r="H1" s="15"/>
-      <c r="I1" s="15"/>
-    </row>
-    <row r="2" spans="1:9" ht="27.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="28" t="s">
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E7" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5">
+        <v>0</v>
+      </c>
+      <c r="G7" s="5">
+        <v>0</v>
+      </c>
+      <c r="H7" s="5">
+        <v>0</v>
+      </c>
+      <c r="I7" s="8">
         <v>1</v>
       </c>
-      <c r="C2" s="27" t="s">
-        <v>2</v>
-      </c>
-      <c r="D2" s="27" t="s">
-        <v>3</v>
-      </c>
-      <c r="E2" s="27" t="s">
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="B8" s="7">
+        <v>12</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E8" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="5">
+        <v>0</v>
+      </c>
+      <c r="G8" s="5">
+        <v>0</v>
+      </c>
+      <c r="H8" s="5">
+        <v>0</v>
+      </c>
+      <c r="I8" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="6" t="s">
+        <v>22</v>
+      </c>
+      <c r="B9" s="7">
+        <v>8</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E9" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F9" s="5">
+        <v>0</v>
+      </c>
+      <c r="G9" s="5">
+        <v>0</v>
+      </c>
+      <c r="H9" s="5">
+        <v>0</v>
+      </c>
+      <c r="I9" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="B10" s="10">
+        <v>8</v>
+      </c>
+      <c r="C10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>7</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="11">
+        <v>0</v>
+      </c>
+      <c r="G10" s="11">
+        <v>0</v>
+      </c>
+      <c r="H10" s="11">
+        <v>0.13</v>
+      </c>
+      <c r="I10" s="12">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="7">
+        <v>8</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E11" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5">
+        <v>0</v>
+      </c>
+      <c r="G11" s="5">
+        <v>0</v>
+      </c>
+      <c r="H11" s="5">
+        <v>0.21</v>
+      </c>
+      <c r="I11" s="13">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="7">
+        <v>12</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E12" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F12" s="5">
+        <v>0</v>
+      </c>
+      <c r="G12" s="5">
+        <v>0</v>
+      </c>
+      <c r="H12" s="5">
+        <v>0.27</v>
+      </c>
+      <c r="I12" s="13">
+        <v>0.73</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B13" s="7">
+        <v>12</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="E13" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5">
+        <v>0</v>
+      </c>
+      <c r="G13" s="5">
+        <v>0</v>
+      </c>
+      <c r="H13" s="5">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="I13" s="13">
+        <v>0.72</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="14" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="15">
+        <v>12</v>
+      </c>
+      <c r="C14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D14" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="16">
+        <v>0</v>
+      </c>
+      <c r="G14" s="16">
+        <v>0</v>
+      </c>
+      <c r="H14" s="16">
+        <v>0.48</v>
+      </c>
+      <c r="I14" s="17">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="B15" s="19">
+        <v>11</v>
+      </c>
+      <c r="C15" s="19" t="s">
+        <v>8</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="E15" s="19" t="s">
+        <v>7</v>
+      </c>
+      <c r="F15" s="20">
+        <v>0</v>
+      </c>
+      <c r="G15" s="20">
+        <v>0</v>
+      </c>
+      <c r="H15" s="20">
+        <v>0.3</v>
+      </c>
+      <c r="I15" s="32">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B16" s="7">
+        <v>12</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E16" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F16" s="5">
+        <v>0</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="H16" s="21">
+        <v>0.94</v>
+      </c>
+      <c r="I16" s="5">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A17" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="B17" s="7">
+        <v>11</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E17" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="F17" s="5">
+        <v>0</v>
+      </c>
+      <c r="G17" s="5">
+        <v>0</v>
+      </c>
+      <c r="H17" s="21">
+        <v>0.93</v>
+      </c>
+      <c r="I17" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A18" s="14" t="s">
+        <v>28</v>
+      </c>
+      <c r="B18" s="15">
+        <v>11</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="F18" s="16">
+        <v>0</v>
+      </c>
+      <c r="G18" s="16">
+        <v>0.28999999999999998</v>
+      </c>
+      <c r="H18" s="22">
+        <v>0.71</v>
+      </c>
+      <c r="I18" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A19" s="6" t="s">
+        <v>30</v>
+      </c>
+      <c r="B19" s="7">
+        <v>6</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E19" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F19" s="5">
+        <v>0</v>
+      </c>
+      <c r="G19" s="23">
+        <v>1</v>
+      </c>
+      <c r="H19" s="5">
+        <v>0</v>
+      </c>
+      <c r="I19" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A20" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="7">
+        <v>9</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F20" s="5">
+        <v>0.01</v>
+      </c>
+      <c r="G20" s="24">
+        <v>0.97</v>
+      </c>
+      <c r="H20" s="5">
+        <v>0.02</v>
+      </c>
+      <c r="I20" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A21" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="7">
+        <v>9</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D21" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F21" s="5">
+        <v>0</v>
+      </c>
+      <c r="G21" s="24">
+        <v>0.93</v>
+      </c>
+      <c r="H21" s="5">
+        <v>7.0000000000000007E-2</v>
+      </c>
+      <c r="I21" s="5">
+        <v>0</v>
+      </c>
+      <c r="L21" s="11"/>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A22" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="7">
+        <v>6</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="E22" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="F22" s="5">
+        <v>0.23</v>
+      </c>
+      <c r="G22" s="24">
+        <v>0.76</v>
+      </c>
+      <c r="H22" s="5">
+        <v>0</v>
+      </c>
+      <c r="I22" s="5">
+        <v>0</v>
+      </c>
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A23" s="14" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="15">
+        <v>11</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="F23" s="16">
+        <v>0</v>
+      </c>
+      <c r="G23" s="25">
+        <v>0.61</v>
+      </c>
+      <c r="H23" s="16">
+        <v>0.39</v>
+      </c>
+      <c r="I23" s="16">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A24" s="18" t="s">
+        <v>35</v>
+      </c>
+      <c r="B24" s="19">
         <v>4</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="C24" s="19" t="s">
+        <v>6</v>
+      </c>
+      <c r="D24" s="19" t="s">
         <v>5</v>
       </c>
-      <c r="G2" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="I2" s="27" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A3" s="33" t="s">
-        <v>15</v>
-      </c>
-      <c r="B3" s="34">
-        <v>12</v>
-      </c>
-      <c r="C3" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="34" t="s">
-        <v>7</v>
-      </c>
-      <c r="E3" s="35" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="36">
-        <v>0</v>
-      </c>
-      <c r="G3" s="36">
-        <v>0</v>
-      </c>
-      <c r="H3" s="36">
-        <v>0</v>
-      </c>
-      <c r="I3" s="37">
+      <c r="E24" s="19" t="s">
+        <v>5</v>
+      </c>
+      <c r="F24" s="20">
+        <v>0.32</v>
+      </c>
+      <c r="G24" s="26">
+        <v>0.68</v>
+      </c>
+      <c r="H24" s="20">
+        <v>0</v>
+      </c>
+      <c r="I24" s="20">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A25" s="6" t="s">
+        <v>33</v>
+      </c>
+      <c r="B25" s="7">
+        <v>7</v>
+      </c>
+      <c r="C25" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F25" s="27">
         <v>1</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A4" s="30" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="2">
-        <v>11</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="7">
-        <v>0</v>
-      </c>
-      <c r="G4" s="7">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7">
-        <v>0.06</v>
-      </c>
-      <c r="I4" s="10">
-        <v>0.94</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A5" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="B5" s="20">
-        <v>11</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D5" s="20" t="s">
-        <v>7</v>
-      </c>
-      <c r="E5" s="21" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="22">
-        <v>0</v>
-      </c>
-      <c r="G5" s="22">
-        <v>0</v>
-      </c>
-      <c r="H5" s="22">
-        <v>0.19</v>
-      </c>
-      <c r="I5" s="38">
-        <v>0.81</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A6" s="30" t="s">
-        <v>17</v>
-      </c>
-      <c r="B6" s="2">
-        <v>8</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="7">
-        <v>0</v>
-      </c>
-      <c r="G6" s="7">
-        <v>0</v>
-      </c>
-      <c r="H6" s="11">
+      <c r="G25" s="5">
+        <v>0</v>
+      </c>
+      <c r="H25" s="5">
+        <v>0</v>
+      </c>
+      <c r="I25" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A26" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="B26" s="7">
+        <v>8</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>5</v>
+      </c>
+      <c r="F26" s="27">
         <v>1</v>
       </c>
-      <c r="I6" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A7" s="30" t="s">
-        <v>18</v>
-      </c>
-      <c r="B7" s="2">
-        <v>11</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F7" s="7">
-        <v>0</v>
-      </c>
-      <c r="G7" s="7">
-        <v>0</v>
-      </c>
-      <c r="H7" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="I7" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A8" s="30" t="s">
-        <v>19</v>
-      </c>
-      <c r="B8" s="2">
-        <v>7</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="E8" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F8" s="7">
-        <v>0</v>
-      </c>
-      <c r="G8" s="7">
-        <v>0</v>
-      </c>
-      <c r="H8" s="9">
-        <v>0.99</v>
-      </c>
-      <c r="I8" s="7">
-        <v>0.01</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A9" s="30" t="s">
+      <c r="G26" s="5">
+        <v>0</v>
+      </c>
+      <c r="H26" s="5">
+        <v>0</v>
+      </c>
+      <c r="I26" s="5">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A27" s="28" t="s">
+        <v>10</v>
+      </c>
+      <c r="B27" s="29">
         <v>9</v>
       </c>
-      <c r="B9" s="2">
-        <v>12</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F9" s="7">
-        <v>0</v>
-      </c>
-      <c r="G9" s="7">
-        <v>0</v>
-      </c>
-      <c r="H9" s="9">
-        <v>0.94</v>
-      </c>
-      <c r="I9" s="7">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A10" s="30" t="s">
-        <v>20</v>
-      </c>
-      <c r="B10" s="2">
-        <v>12</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F10" s="7">
-        <v>0</v>
-      </c>
-      <c r="G10" s="7">
-        <v>0.08</v>
-      </c>
-      <c r="H10" s="9">
-        <v>0.92</v>
-      </c>
-      <c r="I10" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A11" s="30" t="s">
-        <v>21</v>
-      </c>
-      <c r="B11" s="2">
-        <v>12</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F11" s="7">
-        <v>0</v>
-      </c>
-      <c r="G11" s="7">
-        <v>0</v>
-      </c>
-      <c r="H11" s="9">
-        <v>0.77</v>
-      </c>
-      <c r="I11" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A12" s="30" t="s">
-        <v>22</v>
-      </c>
-      <c r="B12" s="2">
-        <v>11</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F12" s="7">
-        <v>0</v>
-      </c>
-      <c r="G12" s="7">
-        <v>0</v>
-      </c>
-      <c r="H12" s="9">
-        <v>0.77</v>
-      </c>
-      <c r="I12" s="7">
-        <v>0.23</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A13" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="B13" s="20">
-        <v>12</v>
-      </c>
-      <c r="C13" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D13" s="20" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="23" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" s="22">
-        <v>0</v>
-      </c>
-      <c r="G13" s="22">
-        <v>0</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.76</v>
-      </c>
-      <c r="I13" s="22">
-        <v>0.24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A14" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="2">
-        <v>11</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="2" t="s">
+      <c r="C27" s="29" t="s">
+        <v>7</v>
+      </c>
+      <c r="D27" s="29" t="s">
         <v>5</v>
       </c>
-      <c r="E14" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F14" s="7">
-        <v>0</v>
-      </c>
-      <c r="G14" s="12">
+      <c r="E27" s="29" t="s">
+        <v>5</v>
+      </c>
+      <c r="F27" s="30">
         <v>1</v>
       </c>
-      <c r="H14" s="7">
-        <v>0</v>
-      </c>
-      <c r="I14" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A15" s="30" t="s">
-        <v>25</v>
-      </c>
-      <c r="B15" s="2">
-        <v>8</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F15" s="7">
-        <v>0.04</v>
-      </c>
-      <c r="G15" s="8">
-        <v>0.92</v>
-      </c>
-      <c r="H15" s="7">
-        <v>0.03</v>
-      </c>
-      <c r="I15" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A16" s="30" t="s">
-        <v>26</v>
-      </c>
-      <c r="B16" s="2">
-        <v>8</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F16" s="7">
-        <v>0</v>
-      </c>
-      <c r="G16" s="8">
-        <v>0.81</v>
-      </c>
-      <c r="H16" s="7">
-        <v>0.19</v>
-      </c>
-      <c r="I16" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A17" s="33" t="s">
-        <v>27</v>
-      </c>
-      <c r="B17" s="34">
-        <v>11</v>
-      </c>
-      <c r="C17" s="34" t="s">
-        <v>8</v>
-      </c>
-      <c r="D17" s="34" t="s">
-        <v>5</v>
-      </c>
-      <c r="E17" s="39" t="s">
-        <v>6</v>
-      </c>
-      <c r="F17" s="36">
-        <v>0</v>
-      </c>
-      <c r="G17" s="40">
-        <v>0.7</v>
-      </c>
-      <c r="H17" s="36">
-        <v>0.3</v>
-      </c>
-      <c r="I17" s="36">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A18" s="30" t="s">
-        <v>28</v>
-      </c>
-      <c r="B18" s="2">
-        <v>8</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="F18" s="7">
-        <v>0</v>
-      </c>
-      <c r="G18" s="8">
-        <v>0.65</v>
-      </c>
-      <c r="H18" s="7">
-        <v>0.35</v>
-      </c>
-      <c r="I18" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A19" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="B19" s="20">
-        <v>12</v>
-      </c>
-      <c r="C19" s="20" t="s">
-        <v>8</v>
-      </c>
-      <c r="D19" s="20" t="s">
-        <v>5</v>
-      </c>
-      <c r="E19" s="25" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" s="22">
-        <v>0</v>
-      </c>
-      <c r="G19" s="26">
-        <v>0.63</v>
-      </c>
-      <c r="H19" s="22">
-        <v>0.37</v>
-      </c>
-      <c r="I19" s="22">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A20" s="30" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="2">
-        <v>7</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E20" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F20" s="13">
-        <v>1</v>
-      </c>
-      <c r="G20" s="7">
-        <v>0</v>
-      </c>
-      <c r="H20" s="7">
-        <v>0</v>
-      </c>
-      <c r="I20" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A21" s="30" t="s">
-        <v>10</v>
-      </c>
-      <c r="B21" s="2">
-        <v>9</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E21" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F21" s="13">
-        <v>1</v>
-      </c>
-      <c r="G21" s="7">
-        <v>0</v>
-      </c>
-      <c r="H21" s="7">
-        <v>0</v>
-      </c>
-      <c r="I21" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A22" s="30" t="s">
-        <v>30</v>
-      </c>
-      <c r="B22" s="2">
-        <v>8</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E22" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F22" s="13">
-        <v>1</v>
-      </c>
-      <c r="G22" s="7">
-        <v>0</v>
-      </c>
-      <c r="H22" s="7">
-        <v>0</v>
-      </c>
-      <c r="I22" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A23" s="30" t="s">
-        <v>11</v>
-      </c>
-      <c r="B23" s="2">
-        <v>9</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E23" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F23" s="13">
-        <v>1</v>
-      </c>
-      <c r="G23" s="7">
-        <v>0</v>
-      </c>
-      <c r="H23" s="7">
-        <v>0</v>
-      </c>
-      <c r="I23" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A24" s="30" t="s">
-        <v>31</v>
-      </c>
-      <c r="B24" s="2">
-        <v>9</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E24" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F24" s="13">
-        <v>1</v>
-      </c>
-      <c r="G24" s="7">
-        <v>0</v>
-      </c>
-      <c r="H24" s="7">
-        <v>0</v>
-      </c>
-      <c r="I24" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A25" s="30" t="s">
-        <v>32</v>
-      </c>
-      <c r="B25" s="2">
-        <v>6</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F25" s="13">
-        <v>1</v>
-      </c>
-      <c r="G25" s="7">
-        <v>0</v>
-      </c>
-      <c r="H25" s="7">
-        <v>0</v>
-      </c>
-      <c r="I25" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A26" s="30" t="s">
-        <v>33</v>
-      </c>
-      <c r="B26" s="2">
-        <v>6</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="E26" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="F26" s="13">
-        <v>1</v>
-      </c>
-      <c r="G26" s="7">
-        <v>0</v>
-      </c>
-      <c r="H26" s="7">
-        <v>0</v>
-      </c>
-      <c r="I26" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" ht="14.25" x14ac:dyDescent="0.2">
-      <c r="A27" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="B27" s="16">
-        <v>4</v>
-      </c>
-      <c r="C27" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="D27" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="E27" s="17" t="s">
-        <v>5</v>
-      </c>
-      <c r="F27" s="18">
-        <v>1</v>
-      </c>
-      <c r="G27" s="19">
-        <v>0</v>
-      </c>
-      <c r="H27" s="19">
-        <v>0</v>
-      </c>
-      <c r="I27" s="19">
+      <c r="G27" s="31">
+        <v>0</v>
+      </c>
+      <c r="H27" s="31">
+        <v>0</v>
+      </c>
+      <c r="I27" s="31">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A14:I19">
-    <sortCondition descending="1" ref="G14:G19"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A25:I27">
+    <sortCondition descending="1" ref="F25:F27"/>
   </sortState>
   <mergeCells count="2">
+    <mergeCell ref="C1:E1"/>
     <mergeCell ref="F1:I1"/>
-    <mergeCell ref="C1:E1"/>
   </mergeCells>
   <conditionalFormatting sqref="C3:E27">
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
-      <formula>"VH"</formula>
+    <cfRule type="cellIs" dxfId="3" priority="1" operator="equal">
+      <formula>"L"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="2" operator="equal">
+      <formula>"M"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="3" operator="equal">
       <formula>"H"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"M"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="1" operator="equal">
-      <formula>"L"</formula>
+    <cfRule type="cellIs" dxfId="0" priority="4" operator="equal">
+      <formula>"VH"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
